--- a/src/electron/crawler/config/小米粒夏日.xlsx
+++ b/src/electron/crawler/config/小米粒夏日.xlsx
@@ -8,19 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\outsider\github\GF_playwright\src\electron\crawler\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E5746D-F060-49AD-87CF-CB3C141D92AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF83F39-A476-47EC-8C7E-863FDF6FC2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="2190" windowWidth="16410" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="6780" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>流水號</t>
   </si>
@@ -28,123 +33,212 @@
     <t>content</t>
   </si>
   <si>
-    <t>【cimYL785】實拍輕薄涼快莫代爾T恤250605</t>
-  </si>
-  <si>
-    <t>F：胸圍 82、肩寬 40、袖長 18、衣長 52
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2776】實拍小眾時髦簡約一片式設計繫帶洋裝250605</t>
-  </si>
-  <si>
-    <t>M：胸圍 92、腰圍 102、肩寬 32、裙長 120
-L：胸圍 96、腰圍 104、肩寬 33、裙長 122
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2770】實拍甜美無袖花邊壓褶背心250605</t>
-  </si>
-  <si>
-    <t>M：胸圍 102、肩寬 38、衣長 66
-L：胸圍 106、肩寬 38、衣長 68
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2769】實拍韓代款氣質圓領老錢風寬鬆上衣2769250605</t>
-  </si>
-  <si>
-    <t>M：胸圍 110、肩寬 55、袖長 25、衣長 77
-L：胸圍 114、肩寬 57、袖長 27、衣長 79
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2775】實拍高級極簡直筒側開叉裙（鬆緊腰）250605</t>
-  </si>
-  <si>
-    <t>M：腰圍 64-80、臀圍 92、裙長 92
-L：腰圍 66-82、臀圍 96、裙長 94
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2761】實拍韓國設計款廓形天然棉寬鬆上衣250605</t>
-  </si>
-  <si>
-    <t>M：胸圍 118、肩寬 57、衣長 69–77
-L：胸圍 122、肩寬 58、衣長 70–78
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim7701】實拍韓國高單老錢風亞麻天然闊腿褲250605</t>
-  </si>
-  <si>
-    <t>M：腰圍 68、臀圍 102、大腿圍 70、褲長 100
-L：腰圍 72、臀圍 106、大腿圍 74、褲長 102
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2756】實拍韓國簡約高級感娃娃衫250605</t>
-  </si>
-  <si>
-    <t>M：胸圍 94、衣長 71、肩寬 33
-L：胸圍 98、衣長 72、肩寬 34
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2758】實拍韓國設計感簡約扭結氣質長洋裝250605</t>
-  </si>
-  <si>
-    <t>短款：胸圍 94、腰圍 104、裙長 117、肩寬 32
-長款：胸圍 94、腰圍 104、裙長 127、肩寬 32
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2762】實拍法式後開叉心機簡約襯衫250605</t>
-  </si>
-  <si>
-    <t>M：胸圍 92、衣長 54、肩寬 47
-L：胸圍 96、衣長 55、肩寬 48
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2759】實拍夏日涼涼天然褶皺肌理A字休閒褲（鬆緊腰）250605</t>
-  </si>
-  <si>
-    <t>M：腰圍 66–72、臀圍 104、大腿圍 60、褲長 90
-L：腰圍 68–74、臀圍 108、大腿圍 64、褲長 91
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2760】實拍韓國氣質肌理收腰綁帶襯衫250605</t>
-  </si>
-  <si>
-    <t>M：胸圍 106、衣長 71、肩寬 69
-L：胸圍 110、衣長 72、肩寬 70
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2765】實拍韓國繫帶氣質天然上衣250605</t>
-  </si>
-  <si>
-    <t>M：胸圍 94、衣長 53–57、肩寬 37
-L：胸圍 98、衣長 53–57、肩寬 37
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2757】實拍法式慵懶點點雪紡闊腿褲（鬆緊腰，有口袋）250605</t>
-  </si>
-  <si>
-    <t>M：腰圍 60–72、臀圍 100、大腿圍 72、褲長 103
-L：腰圍 62–74、臀圍 104、大腿圍 76、褲長 104
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2755】實拍夏天氛圍感顯瘦混棉休閒褲（鬆緊腰，腰帶可拆）250605</t>
-  </si>
-  <si>
-    <t>M：腰圍 62–74、臀圍 104、大腿圍 82、褲長 94
-L：腰圍 64–76、臀圍 108、大腿圍 86、褲長 95
-誤差 1–3 公分為正常，以實物為準。</t>
+    <t>【Y20163】實拍初秋百搭舒適必備紐扣棉質長袖T恤250827</t>
+  </si>
+  <si>
+    <t>F：肩寬 34、袖長 59、胸圍 86、下擺圍 86、衣長 54
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y20169】實拍初秋懶綁帶長袖針織衫250827</t>
+  </si>
+  <si>
+    <t>F：肩寬 38、袖長 61、胸圍 88、下擺圍 92、衣長 60
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y26292】實拍初秋美式廓形挺版顯瘦氣球褲250827</t>
+  </si>
+  <si>
+    <t>M：腰圍 60、臀圍 110、大腿圍 74、褲腳圍 66、褲長 99
+L：腰圍 64、臀圍 114、大腿圍 76、褲腳圍 68、褲長 100
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y502】實拍初秋法式簡約扭結針織洋裝250827</t>
+  </si>
+  <si>
+    <t>F：胸圍 80、腰圍 84、衣長 110
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y518】實拍初秋復古麻花polo針織衫250827</t>
+  </si>
+  <si>
+    <t>F：肩寬 35、袖長 23、胸圍 78、下擺圍 58、衣長 53
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y527】實拍初秋韓系簡約條紋短袖針織T恤（羊毛6%）250827</t>
+  </si>
+  <si>
+    <t>F：肩寬 37、袖長 21、胸圍 88、下擺圍 74、衣長 50
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y529】實拍初秋氣質一字肩針織衫250827</t>
+  </si>
+  <si>
+    <t>F：肩寬 46、袖長 51、胸圍 94、下擺圍 60、衣長 50
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y712】實拍初秋經典舒適款加厚磨毛圓領T恤250827</t>
+  </si>
+  <si>
+    <t>F：肩寬 40、袖長 19、胸圍 94、下擺圍 98、衣長 56
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y79786】實拍初秋美式復古高級感PU夾克皮衣250827</t>
+  </si>
+  <si>
+    <t>F：袖長 75、胸圍 134、下擺圍 92、衣長 57
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y8011】實拍初秋休閒超顯瘦氣球牛仔褲（亞麻5%）250827</t>
+  </si>
+  <si>
+    <t>S：腰圍 63、臀圍 96、大腿圍 66、褲腳圍 66、褲長 100
+M：腰圍 67、臀圍 100、大腿圍 68、褲腳圍 68、褲長 101
+L：腰圍 71、臀圍 104、大腿圍 70、褲腳圍 70、褲長 102
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82561】實拍初秋氣質無領墊肩西裝外套250827</t>
+  </si>
+  <si>
+    <t>M：肩寬 41、袖長 59、胸圍 110、下擺圍 112、衣長 72
+L：肩寬 42、袖長 60、胸圍 114、下擺圍 116、衣長 73
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82571】實拍初秋法式設計款襯衫（天絲30%）250827</t>
+  </si>
+  <si>
+    <t>M：肩寬 50、袖長 51、胸圍 114、下擺圍 114、衣長 67/71
+L：肩寬 51、袖長 52、胸圍 118、下擺圍 118、衣長 68/72
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82572】實拍初秋氣質斜肩設計款長袖T恤250827</t>
+  </si>
+  <si>
+    <t>F：袖長 53、胸圍 82、下擺圍 76、衣長 58
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82573】實拍初秋法式薄領收腰T恤+高腰垂感拖地長褲 2件套250827</t>
+  </si>
+  <si>
+    <t>M(上衣)：肩寬 45、袖長 58、胸圍 78、腰圍 60、衣長 58
+L(上衣)：肩寬 46、袖長 59、胸圍 82、腰圍 64、衣長 59
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82576】實拍初秋復古大擺A字牛仔裙250827</t>
+  </si>
+  <si>
+    <t>M：腰圍 68、臀圍 98、裙長 96
+L：腰圍 72、臀圍 102、裙長 97
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82578】實拍初秋法式輕奢氣質斜門襟襯衫（30%天絲）250827</t>
+  </si>
+  <si>
+    <t>M：肩寬 48、袖長 50、胸圍 110、下擺圍 112、衣長 69
+L：肩寬 49、袖長 51、胸圍 114、下擺圍 116、衣長 70
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82579】實拍初秋高腰顯瘦直筒後開衩西裝褲250827</t>
+  </si>
+  <si>
+    <t>S：腰圍 62、臀圍 86、下擺圍 86、褲長 97
+M：腰圍 66、臀圍 90、下擺圍 90、褲長 98
+L：腰圍 70、臀圍 94、下擺圍 94、褲長 99
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82580】實拍初秋大氣場超瘦腿西裝褲含腰帶250827</t>
+  </si>
+  <si>
+    <t>M：腰圍 68、臀圍 102、大腿圍 68、褲腳圍 56、褲長 99
+L：腰圍 72、臀圍 106、大腿圍 70、褲腳圍 60、褲長 100
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82581】實拍初秋法式氣質肌理飄帶長袖襯衫（桑蠶絲6%）250827</t>
+  </si>
+  <si>
+    <t>M：肩寬 39、袖長 56、胸圍 106、下擺圍 102、衣長 70
+L：肩寬 40、袖長 57、胸圍 110、下擺圍 106、衣長 71
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82582】實拍初秋法式輕熟高級感優雅飄帶襯衫（80%莫代爾）250827</t>
+  </si>
+  <si>
+    <t>M：肩寬 38、袖長 60、胸圍 104、下擺圍 110、衣長 60/71
+L：肩寬 39、袖長 61、胸圍 108、下擺圍 114、衣長 61/72
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82583】實拍初秋日系挺料純棉圓領襯衫250827</t>
+  </si>
+  <si>
+    <t>M：肩寬 60、袖長 50、胸圍 124、下擺圍 132、衣長 63
+L：肩寬 61、袖長 51、胸圍 128、下擺圍 136、衣長 64
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82585】實拍初秋英倫風立領休閒綁帶風衣外套250827</t>
+  </si>
+  <si>
+    <t>M：袖長 66、胸圍 122、下擺圍 132、衣長 76
+L：袖長 67、胸圍 126、下擺圍 136、衣長 77
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y865】實拍初秋垂感流蘇針織洋裝250827</t>
+  </si>
+  <si>
+    <t>F：肩寬 30、胸圍 78、腰圍 82、衣長 105
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y9815】實拍初秋超顯瘦高腰闊腿西裝褲250827</t>
+  </si>
+  <si>
+    <t>S：腰圍 64、臀圍 90、大腿圍 66、褲腳圍 102、褲長 99
+M：腰圍 68、臀圍 94、大腿圍 68、褲腳圍 103、褲長 100
+L：腰圍 72、臀圍 98、大腿圍 70、褲腳圍 104、褲長 101
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y9816】實拍初秋高質感天絲棉設計款西裝褲250827</t>
+  </si>
+  <si>
+    <t>M：腰圍 68、臀圍 100、大腿圍 70、褲腳圍 76、褲長 98
+L：腰圍 72、臀圍 104、大腿圍 72、褲腳圍 78、褲長 99
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y9863】實拍初秋復古法式內襯格子PU皮背心250827</t>
+  </si>
+  <si>
+    <t>M：肩寬 47、胸圍 120、下擺圍 126、衣長 60
+L：肩寬 48、胸圍 124、下擺圍 130、衣長 61
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y2501】實拍初秋簡約時髦銀色金屬針釦PU皮250827</t>
+  </si>
+  <si>
+    <t>材质：PU皮(合金扣头)
+尺寸：100*1.3 cm</t>
   </si>
 </sst>
 </file>
@@ -205,12 +299,12 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="PingFang TC"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <name val="PingFang SC"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
     </font>
@@ -241,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -270,16 +364,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -577,7 +674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="63.75">
+    <row r="2" spans="1:3" ht="85.9">
       <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
@@ -586,7 +683,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="89.25">
+    <row r="3" spans="1:3" ht="85.9">
       <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
@@ -595,7 +692,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" ht="89.25">
+    <row r="4" spans="1:3" ht="128.65">
       <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
@@ -604,7 +701,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" ht="89.25">
+    <row r="5" spans="1:3" ht="71.650000000000006">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -613,7 +710,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" ht="89.25">
+    <row r="6" spans="1:3" ht="85.9">
       <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
@@ -622,7 +719,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" ht="89.25">
+    <row r="7" spans="1:3" ht="85.9">
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
@@ -631,7 +728,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" ht="114.75">
+    <row r="8" spans="1:3" ht="85.9">
       <c r="A8" s="10" t="s">
         <v>14</v>
       </c>
@@ -640,8 +737,8 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" ht="89.25">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:3" ht="85.9">
+      <c r="A9" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -649,17 +746,17 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="89.25">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:3" ht="85.9">
+      <c r="A10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" ht="89.25">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:3" ht="171.4">
+      <c r="A11" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -667,26 +764,26 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" ht="89.25">
+    <row r="12" spans="1:3" ht="121.5">
       <c r="A12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" ht="89.25">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:3" ht="121.5">
+      <c r="A13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" ht="89.25">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:3" ht="71.650000000000006">
+      <c r="A14" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -694,8 +791,8 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" ht="114.75">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:3" ht="128.65">
+      <c r="A15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="11" t="s">
@@ -703,73 +800,121 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" ht="89.25">
+    <row r="16" spans="1:3" ht="94.5">
       <c r="A16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8"/>
+    <row r="17" spans="1:3" ht="121.5">
+      <c r="A17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8"/>
+    <row r="18" spans="1:3" ht="128.65">
+      <c r="A18" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8"/>
+    <row r="19" spans="1:3" ht="128.65">
+      <c r="A19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>37</v>
+      </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8"/>
+    <row r="20" spans="1:3" ht="128.65">
+      <c r="A20" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>39</v>
+      </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
+    <row r="21" spans="1:3" ht="121.5">
+      <c r="A21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>41</v>
+      </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="8"/>
+    <row r="22" spans="1:3" ht="128.65">
+      <c r="A22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="8"/>
+    <row r="23" spans="1:3" ht="128.65">
+      <c r="A23" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="8"/>
+    <row r="24" spans="1:3" ht="71.650000000000006">
+      <c r="A24" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
+    <row r="25" spans="1:3" ht="171.4">
+      <c r="A25" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="8"/>
+    <row r="26" spans="1:3" ht="121.5">
+      <c r="A26" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="8"/>
+    <row r="27" spans="1:3" ht="128.65">
+      <c r="A27" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="8"/>
+    <row r="28" spans="1:3" ht="27">
+      <c r="A28" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3">

--- a/src/electron/crawler/config/小米粒夏日.xlsx
+++ b/src/electron/crawler/config/小米粒夏日.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\outsider\github\GF_playwright\src\electron\crawler\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF83F39-A476-47EC-8C7E-863FDF6FC2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4AEC94-1763-4D81-98F7-37395885DDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="6780" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>流水號</t>
   </si>
@@ -33,212 +33,163 @@
     <t>content</t>
   </si>
   <si>
-    <t>【Y20163】實拍初秋百搭舒適必備紐扣棉質長袖T恤250827</t>
-  </si>
-  <si>
-    <t>F：肩寬 34、袖長 59、胸圍 86、下擺圍 86、衣長 54
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y20169】實拍初秋懶綁帶長袖針織衫250827</t>
-  </si>
-  <si>
-    <t>F：肩寬 38、袖長 61、胸圍 88、下擺圍 92、衣長 60
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y26292】實拍初秋美式廓形挺版顯瘦氣球褲250827</t>
-  </si>
-  <si>
-    <t>M：腰圍 60、臀圍 110、大腿圍 74、褲腳圍 66、褲長 99
-L：腰圍 64、臀圍 114、大腿圍 76、褲腳圍 68、褲長 100
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y502】實拍初秋法式簡約扭結針織洋裝250827</t>
-  </si>
-  <si>
-    <t>F：胸圍 80、腰圍 84、衣長 110
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y518】實拍初秋復古麻花polo針織衫250827</t>
-  </si>
-  <si>
-    <t>F：肩寬 35、袖長 23、胸圍 78、下擺圍 58、衣長 53
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y527】實拍初秋韓系簡約條紋短袖針織T恤（羊毛6%）250827</t>
-  </si>
-  <si>
-    <t>F：肩寬 37、袖長 21、胸圍 88、下擺圍 74、衣長 50
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y529】實拍初秋氣質一字肩針織衫250827</t>
-  </si>
-  <si>
-    <t>F：肩寬 46、袖長 51、胸圍 94、下擺圍 60、衣長 50
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y712】實拍初秋經典舒適款加厚磨毛圓領T恤250827</t>
-  </si>
-  <si>
-    <t>F：肩寬 40、袖長 19、胸圍 94、下擺圍 98、衣長 56
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y79786】實拍初秋美式復古高級感PU夾克皮衣250827</t>
-  </si>
-  <si>
-    <t>F：袖長 75、胸圍 134、下擺圍 92、衣長 57
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y8011】實拍初秋休閒超顯瘦氣球牛仔褲（亞麻5%）250827</t>
-  </si>
-  <si>
-    <t>S：腰圍 63、臀圍 96、大腿圍 66、褲腳圍 66、褲長 100
-M：腰圍 67、臀圍 100、大腿圍 68、褲腳圍 68、褲長 101
-L：腰圍 71、臀圍 104、大腿圍 70、褲腳圍 70、褲長 102
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82561】實拍初秋氣質無領墊肩西裝外套250827</t>
-  </si>
-  <si>
-    <t>M：肩寬 41、袖長 59、胸圍 110、下擺圍 112、衣長 72
-L：肩寬 42、袖長 60、胸圍 114、下擺圍 116、衣長 73
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82571】實拍初秋法式設計款襯衫（天絲30%）250827</t>
-  </si>
-  <si>
-    <t>M：肩寬 50、袖長 51、胸圍 114、下擺圍 114、衣長 67/71
-L：肩寬 51、袖長 52、胸圍 118、下擺圍 118、衣長 68/72
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82572】實拍初秋氣質斜肩設計款長袖T恤250827</t>
-  </si>
-  <si>
-    <t>F：袖長 53、胸圍 82、下擺圍 76、衣長 58
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82573】實拍初秋法式薄領收腰T恤+高腰垂感拖地長褲 2件套250827</t>
-  </si>
-  <si>
-    <t>M(上衣)：肩寬 45、袖長 58、胸圍 78、腰圍 60、衣長 58
-L(上衣)：肩寬 46、袖長 59、胸圍 82、腰圍 64、衣長 59
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82576】實拍初秋復古大擺A字牛仔裙250827</t>
-  </si>
-  <si>
-    <t>M：腰圍 68、臀圍 98、裙長 96
-L：腰圍 72、臀圍 102、裙長 97
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82578】實拍初秋法式輕奢氣質斜門襟襯衫（30%天絲）250827</t>
-  </si>
-  <si>
-    <t>M：肩寬 48、袖長 50、胸圍 110、下擺圍 112、衣長 69
-L：肩寬 49、袖長 51、胸圍 114、下擺圍 116、衣長 70
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82579】實拍初秋高腰顯瘦直筒後開衩西裝褲250827</t>
-  </si>
-  <si>
-    <t>S：腰圍 62、臀圍 86、下擺圍 86、褲長 97
-M：腰圍 66、臀圍 90、下擺圍 90、褲長 98
-L：腰圍 70、臀圍 94、下擺圍 94、褲長 99
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82580】實拍初秋大氣場超瘦腿西裝褲含腰帶250827</t>
-  </si>
-  <si>
-    <t>M：腰圍 68、臀圍 102、大腿圍 68、褲腳圍 56、褲長 99
-L：腰圍 72、臀圍 106、大腿圍 70、褲腳圍 60、褲長 100
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82581】實拍初秋法式氣質肌理飄帶長袖襯衫（桑蠶絲6%）250827</t>
-  </si>
-  <si>
-    <t>M：肩寬 39、袖長 56、胸圍 106、下擺圍 102、衣長 70
-L：肩寬 40、袖長 57、胸圍 110、下擺圍 106、衣長 71
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82582】實拍初秋法式輕熟高級感優雅飄帶襯衫（80%莫代爾）250827</t>
-  </si>
-  <si>
-    <t>M：肩寬 38、袖長 60、胸圍 104、下擺圍 110、衣長 60/71
-L：肩寬 39、袖長 61、胸圍 108、下擺圍 114、衣長 61/72
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82583】實拍初秋日系挺料純棉圓領襯衫250827</t>
-  </si>
-  <si>
-    <t>M：肩寬 60、袖長 50、胸圍 124、下擺圍 132、衣長 63
-L：肩寬 61、袖長 51、胸圍 128、下擺圍 136、衣長 64
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82585】實拍初秋英倫風立領休閒綁帶風衣外套250827</t>
-  </si>
-  <si>
-    <t>M：袖長 66、胸圍 122、下擺圍 132、衣長 76
-L：袖長 67、胸圍 126、下擺圍 136、衣長 77
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y865】實拍初秋垂感流蘇針織洋裝250827</t>
-  </si>
-  <si>
-    <t>F：肩寬 30、胸圍 78、腰圍 82、衣長 105
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y9815】實拍初秋超顯瘦高腰闊腿西裝褲250827</t>
-  </si>
-  <si>
-    <t>S：腰圍 64、臀圍 90、大腿圍 66、褲腳圍 102、褲長 99
-M：腰圍 68、臀圍 94、大腿圍 68、褲腳圍 103、褲長 100
-L：腰圍 72、臀圍 98、大腿圍 70、褲腳圍 104、褲長 101
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y9816】實拍初秋高質感天絲棉設計款西裝褲250827</t>
-  </si>
-  <si>
-    <t>M：腰圍 68、臀圍 100、大腿圍 70、褲腳圍 76、褲長 98
-L：腰圍 72、臀圍 104、大腿圍 72、褲腳圍 78、褲長 99
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y9863】實拍初秋復古法式內襯格子PU皮背心250827</t>
-  </si>
-  <si>
-    <t>M：肩寬 47、胸圍 120、下擺圍 126、衣長 60
-L：肩寬 48、胸圍 124、下擺圍 130、衣長 61
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y2501】實拍初秋簡約時髦銀色金屬針釦PU皮250827</t>
-  </si>
-  <si>
-    <t>材质：PU皮(合金扣头)
-尺寸：100*1.3 cm</t>
+    <t>【Y8058】實拍初秋復古質感皮衣外套250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 44、胸圍 102、下擺圍 95、衣長 56
+L：肩寬 45、胸圍 106、下擺圍 99、衣長 57
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y80600】實拍小眾寬鬆大翻領風衣外套250828</t>
+  </si>
+  <si>
+    <t>M：胸圍 140、腰圍 142、袖長 73、衣長 80
+L：胸圍 144、腰圍 146、袖長 74、衣長 81
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82588】 實拍韓系高級感氛質天然襯衫250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 47、袖長 54、胸圍 116、下擺圍 116、衣長 69/74
+L：肩寬 48、袖長 55、胸圍 120、下擺圍 120、衣長 70/75
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82592】 實拍法式復古氛質收腰襯衫含腰帶250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 50、袖長 55、胸圍 124、下擺圍 130、衣長 62
+L：肩寬 51、袖長 56、胸圍 128、下擺圍 134、衣長 63
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82593】 實拍法式復古微高領襯衫長洋裝含腰帶250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 53、袖長 55、胸圍 138、腰圍 142、衣長 123
+L：肩寬 54、袖長 56、胸圍 142、腰圍 146、衣長 124
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82595】實拍正反兩面可穿秋季英倫格子拼接風衣外套250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 56、袖長 52、胸圍 134、下擺圍 154、衣長 75
+L：肩寬 57、袖長 53、胸圍 138、下擺圍 158、衣長 76
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82596】實拍韓式懶懶一字肩條紋長袖T恤250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 46、袖長 57、胸圍 84、腰圍 60、衣長 60
+L：肩寬 47、袖長 58、胸圍 88、腰圍 64、衣長 61
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82597】 實拍初秋男友款直條長袖襯衫寬鬆襯衫250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 50、袖長 54、胸圍 118、下擺圍 124、衣長 71/76
+L：肩寬 51、袖長 55、胸圍 122、下擺圍 128、衣長 72/77
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82598】實拍秋季韓系復古翻領一粒扣大衣外套250828</t>
+  </si>
+  <si>
+    <t>M：胸圍 140、腰圍 142、袖長 70、衣長 120
+L：胸圍 144、腰圍 146、袖長 71、衣長 121
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82603】 實拍韓系慵懶工裝雙口袋收腰襯衫含腰帶250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 73、袖長 42、胸圍 114、下擺圍 97、衣長 62/67
+L：肩寬 74、袖長 43、胸圍 118、下擺圍 101、衣長 63/68
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82605】實拍韓系設計款大翻領寬鬆長款風衣外套含腰帶250828</t>
+  </si>
+  <si>
+    <t>M：胸圍 144、下擺圍 146、袖長 71、衣長 110
+L：胸圍 148、下擺圍 150、袖長 72、衣長 111
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y713】實拍初秋氣質半高領背心+長袖針織外套 2件套250828</t>
+  </si>
+  <si>
+    <t>M(背心)：肩寬 33、胸圍 78、腰圍 68、衣長 51
+L(背心)：肩寬 34、胸圍 82、腰圍 72、衣長 52
+M(外套)：肩寬 36、袖長 52、胸圍 84、下擺圍 78、衣長 49
+L(外套)：肩寬 37、袖長 53、胸圍 88、下擺圍 72、衣長 50
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82606】實拍初秋休閒寬鬆懶懶大翻領長款風衣外套含腰帶250828</t>
+  </si>
+  <si>
+    <t>M：胸圍 162、下擺圍 164、袖長 73、衣長 128
+L：胸圍 166、下擺圍 168、袖長 74、衣長 129
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y9821】 實拍秋季慵懶抽繩休閒氣球褲250828</t>
+  </si>
+  <si>
+    <t>M：腰圍 66、臀圍 110、大腿圍 80、褲腳圍 62、褲長 100
+L：腰圍 70、臀圍 114、大腿圍 82、褲腳圍 64、褲長 101
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YH8526】實拍M~XL初秋高腰顯瘦寬鬆褲裙（含羊毛2%）250828</t>
+  </si>
+  <si>
+    <t>M：腰圍 66、臀圍 98、大腿圍 64、褲腳圍 64、褲長 35
+L：腰圍 70、臀圍 102、大腿圍 66、褲腳圍 66、褲長 36
+XL：腰圍 74、臀圍 106、大腿圍 68、褲腳圍 68、褲長 37
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YH9861】實拍初秋設計款腰綁帶條紋襯衫250828</t>
+  </si>
+  <si>
+    <t>M：肩寬 50、袖長 53、胸圍 118、下擺圍 114、衣長 71
+L：肩寬 51、袖長 54、胸圍 122、下擺圍 118、衣長 72
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP117】 實拍初秋柔軟純色V領針織背心250828</t>
+  </si>
+  <si>
+    <t>F：肩寬 40、胸圍 120、下擺圍 126、衣長 58
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP2506】實拍韓系薄款多色圓領針織衫（羊毛6%）250828</t>
+  </si>
+  <si>
+    <t>F：肩寬 37、袖長 60、胸圍 92、下擺圍 92、衣長 56
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP568】 實拍初秋薄款氣質V領針織衫250828</t>
+  </si>
+  <si>
+    <t>F：肩寬 32、袖長 65、胸圍 58、下擺圍 60、衣長 56
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP589】 實拍氣質U領長袖針織衫(羊毛6%)250828</t>
+  </si>
+  <si>
+    <t>F：肩寬 36、袖長 61、胸圍 72、腰圍 58、衣長 54
+誤差 1–3 公分為正常，以實物為準。</t>
   </si>
 </sst>
 </file>
@@ -674,247 +625,219 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="85.9">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:3" ht="141.75">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="85.9">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:3" ht="110.25">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" ht="128.65">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:3" ht="141.75">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" ht="71.650000000000006">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:3" ht="141.75">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" ht="85.9">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:3" ht="141.75">
+      <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" ht="85.9">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:3" ht="141.75">
+      <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" ht="85.9">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:3" ht="141.75">
+      <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" ht="85.9">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:3" ht="141.75">
+      <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="85.9">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:3" ht="141.75">
+      <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" ht="171.4">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:3" ht="141.75">
+      <c r="A11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" ht="121.5">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:3" ht="141.75">
+      <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" ht="121.5">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:3" ht="267.75">
+      <c r="A13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" ht="71.650000000000006">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:3" ht="141.75">
+      <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" ht="128.65">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:3" ht="173.25">
+      <c r="A15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" ht="94.5">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:3" ht="236.25">
+      <c r="A16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" ht="121.5">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:3" ht="141.75">
+      <c r="A17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" ht="128.65">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:3" ht="94.5">
+      <c r="A18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" ht="128.65">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:3" ht="94.5">
+      <c r="A19" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" ht="128.65">
-      <c r="A20" s="10" t="s">
+    <row r="20" spans="1:3" ht="94.5">
+      <c r="A20" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" ht="121.5">
-      <c r="A21" s="12" t="s">
+    <row r="21" spans="1:3" ht="94.5">
+      <c r="A21" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" ht="128.65">
-      <c r="A22" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>43</v>
-      </c>
+    <row r="22" spans="1:3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" ht="128.65">
-      <c r="A23" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>45</v>
-      </c>
+    <row r="23" spans="1:3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" ht="71.650000000000006">
-      <c r="A24" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>47</v>
-      </c>
+    <row r="24" spans="1:3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="171.4">
-      <c r="A25" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>49</v>
-      </c>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="121.5">
-      <c r="A26" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>51</v>
-      </c>
+    <row r="26" spans="1:3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" ht="128.65">
-      <c r="A27" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>53</v>
-      </c>
+    <row r="27" spans="1:3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" ht="27">
-      <c r="A28" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>55</v>
-      </c>
+    <row r="28" spans="1:3">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3">

--- a/src/electron/crawler/config/小米粒夏日.xlsx
+++ b/src/electron/crawler/config/小米粒夏日.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\outsider\github\GF_playwright\src\electron\crawler\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4AEC94-1763-4D81-98F7-37395885DDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1A1888-CE9A-427A-8D1A-388265E39782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>流水號</t>
   </si>
@@ -33,162 +33,194 @@
     <t>content</t>
   </si>
   <si>
-    <t>【Y8058】實拍初秋復古質感皮衣外套250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 44、胸圍 102、下擺圍 95、衣長 56
-L：肩寬 45、胸圍 106、下擺圍 99、衣長 57
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y80600】實拍小眾寬鬆大翻領風衣外套250828</t>
-  </si>
-  <si>
-    <t>M：胸圍 140、腰圍 142、袖長 73、衣長 80
-L：胸圍 144、腰圍 146、袖長 74、衣長 81
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82588】 實拍韓系高級感氛質天然襯衫250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 47、袖長 54、胸圍 116、下擺圍 116、衣長 69/74
-L：肩寬 48、袖長 55、胸圍 120、下擺圍 120、衣長 70/75
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82592】 實拍法式復古氛質收腰襯衫含腰帶250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 50、袖長 55、胸圍 124、下擺圍 130、衣長 62
-L：肩寬 51、袖長 56、胸圍 128、下擺圍 134、衣長 63
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82593】 實拍法式復古微高領襯衫長洋裝含腰帶250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 53、袖長 55、胸圍 138、腰圍 142、衣長 123
-L：肩寬 54、袖長 56、胸圍 142、腰圍 146、衣長 124
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82595】實拍正反兩面可穿秋季英倫格子拼接風衣外套250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 56、袖長 52、胸圍 134、下擺圍 154、衣長 75
-L：肩寬 57、袖長 53、胸圍 138、下擺圍 158、衣長 76
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82596】實拍韓式懶懶一字肩條紋長袖T恤250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 46、袖長 57、胸圍 84、腰圍 60、衣長 60
-L：肩寬 47、袖長 58、胸圍 88、腰圍 64、衣長 61
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82597】 實拍初秋男友款直條長袖襯衫寬鬆襯衫250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 50、袖長 54、胸圍 118、下擺圍 124、衣長 71/76
-L：肩寬 51、袖長 55、胸圍 122、下擺圍 128、衣長 72/77
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82598】實拍秋季韓系復古翻領一粒扣大衣外套250828</t>
-  </si>
-  <si>
-    <t>M：胸圍 140、腰圍 142、袖長 70、衣長 120
-L：胸圍 144、腰圍 146、袖長 71、衣長 121
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82603】 實拍韓系慵懶工裝雙口袋收腰襯衫含腰帶250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 73、袖長 42、胸圍 114、下擺圍 97、衣長 62/67
-L：肩寬 74、袖長 43、胸圍 118、下擺圍 101、衣長 63/68
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82605】實拍韓系設計款大翻領寬鬆長款風衣外套含腰帶250828</t>
-  </si>
-  <si>
-    <t>M：胸圍 144、下擺圍 146、袖長 71、衣長 110
-L：胸圍 148、下擺圍 150、袖長 72、衣長 111
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y713】實拍初秋氣質半高領背心+長袖針織外套 2件套250828</t>
-  </si>
-  <si>
-    <t>M(背心)：肩寬 33、胸圍 78、腰圍 68、衣長 51
-L(背心)：肩寬 34、胸圍 82、腰圍 72、衣長 52
-M(外套)：肩寬 36、袖長 52、胸圍 84、下擺圍 78、衣長 49
-L(外套)：肩寬 37、袖長 53、胸圍 88、下擺圍 72、衣長 50
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y82606】實拍初秋休閒寬鬆懶懶大翻領長款風衣外套含腰帶250828</t>
-  </si>
-  <si>
-    <t>M：胸圍 162、下擺圍 164、袖長 73、衣長 128
-L：胸圍 166、下擺圍 168、袖長 74、衣長 129
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【Y9821】 實拍秋季慵懶抽繩休閒氣球褲250828</t>
-  </si>
-  <si>
-    <t>M：腰圍 66、臀圍 110、大腿圍 80、褲腳圍 62、褲長 100
-L：腰圍 70、臀圍 114、大腿圍 82、褲腳圍 64、褲長 101
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【YH8526】實拍M~XL初秋高腰顯瘦寬鬆褲裙（含羊毛2%）250828</t>
-  </si>
-  <si>
-    <t>M：腰圍 66、臀圍 98、大腿圍 64、褲腳圍 64、褲長 35
-L：腰圍 70、臀圍 102、大腿圍 66、褲腳圍 66、褲長 36
-XL：腰圍 74、臀圍 106、大腿圍 68、褲腳圍 68、褲長 37
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【YH9861】實拍初秋設計款腰綁帶條紋襯衫250828</t>
-  </si>
-  <si>
-    <t>M：肩寬 50、袖長 53、胸圍 118、下擺圍 114、衣長 71
-L：肩寬 51、袖長 54、胸圍 122、下擺圍 118、衣長 72
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【YP117】 實拍初秋柔軟純色V領針織背心250828</t>
-  </si>
-  <si>
-    <t>F：肩寬 40、胸圍 120、下擺圍 126、衣長 58
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【YP2506】實拍韓系薄款多色圓領針織衫（羊毛6%）250828</t>
-  </si>
-  <si>
-    <t>F：肩寬 37、袖長 60、胸圍 92、下擺圍 92、衣長 56
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【YP568】 實拍初秋薄款氣質V領針織衫250828</t>
-  </si>
-  <si>
-    <t>F：肩寬 32、袖長 65、胸圍 58、下擺圍 60、衣長 56
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【YP589】 實拍氣質U領長袖針織衫(羊毛6%)250828</t>
-  </si>
-  <si>
-    <t>F：肩寬 36、袖長 61、胸圍 72、腰圍 58、衣長 54
+    <t>【cim038】實拍韓國QQ羊毛針織長背心（含羊毛13%）250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 94、肩寬 35、衣長 75
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim1258】實拍高級感簡約復古軟皮大容量單肩包250904</t>
+  </si>
+  <si>
+    <t>F：寬 46、高 24、底部 11
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim258】實拍韓國初秋小荷葉親膚天絲針織衫250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 94、肩寬 37、袖長 59、衣長 56
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim2795】實拍設計款收腰繫帶長袖襯衫（純棉）250904</t>
+  </si>
+  <si>
+    <t>M：胸圍 106、肩寬 44、袖長 57、衣長 56
+L：胸圍 110、肩寬 46、袖長 59、衣長 58
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim2796】實拍立領工裝抽繩寬鬆短風衣外套250904</t>
+  </si>
+  <si>
+    <t>M：胸圍 140、肩寬 59、袖長 52、衣長 54
+L：胸圍 144、肩寬 60、袖長 53、衣長 56
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim2797】實拍舒適慵懶天絲混棉闊腿鬆緊刀褲250904</t>
+  </si>
+  <si>
+    <t>M：腰圍 66–82、臀圍 126、大腿圍 80、褲長 97
+L：腰圍 70–86、臀圍 130、大腿圍 84、褲長 99
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim2798】實拍重工韓國設計款斜紋棉工裝褲250904</t>
+  </si>
+  <si>
+    <t>M：腰圍 66-78、臀圍 98、褲長 84
+L：腰圍 68-80、臀圍 102、褲長 86
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim2799】實拍鬆緊腰下襬荷葉PU皮長褲250904</t>
+  </si>
+  <si>
+    <t>M：腰圍 64–82、臀圍 102、褲長 82
+L：腰圍 68–86、臀圍 106、褲長 84
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim519】實拍復古Polo領短袖針織衫+百褶短裙 套裝（羊毛6%）</t>
+  </si>
+  <si>
+    <t>上衣F：胸圍 86、肩寬 35、袖長 18、衣長 54
+半身裙：腰圍 62-76、臀圍 86、裙長 41
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim527】實拍初秋復古條紋POLO針織衫250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 90、肩寬 37、袖長 20、衣長 51
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim61601】實拍韓國極簡柔軟皮質單肩水桶包</t>
+  </si>
+  <si>
+    <t>F：寬 22、高 23、底部 17
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim6607】實拍韓國親膚棉羊6%針織背心250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 94、肩寬 36、衣長 57
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim677】實拍掛脖背心+圓領針織衫（含羊毛6%）250904</t>
+  </si>
+  <si>
+    <t>針織長袖F：胸圍 78、肩寬 35、袖長 55、衣長 54
+背心F：衣長 48
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim687】實拍慵懶深V鏤空針織罩衫+吊帶背心250904</t>
+  </si>
+  <si>
+    <t>針織罩衫F：胸圍 118、肩寬 63、袖長 49、衣長 48
+吊帶F：胸圍 70、衣長 47
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim695】實拍低調高級感的羊毛針織衫（含羊毛6%）250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 90、肩寬 38、袖長 54、衣長 51
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim698】實拍斜肩設計款顯瘦針織衫250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 72、肩寬 35、袖長 64、衣長 54
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim801】實拍高級感貝殼扣亨利款針織衫250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 72、肩寬 33、袖長 59、衣長 55
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim818】實拍韓系簡約鬆弛感披肩針織外套（含羊毛6%）250904</t>
+  </si>
+  <si>
+    <t>F：肩寬 36、袖長 60、衣長 54
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim8911】實拍絕美小眾復古軟皮大容量腋下托特包LD8911</t>
+  </si>
+  <si>
+    <t>F：寬 53、高 21、底部 39*14
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim907】實拍設計感一字肩顯瘦針織衫250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 70、袖長 59、衣長 54
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cimMB766】實拍慵懶復古中性寬鬆條紋POLO針織衫250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 108、肩寬 55、袖長 43、衣長 61
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cimMB775】實拍簡約中性條紋針織背心250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 90、肩寬 36、衣長 47
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cimOUT935】實拍高級感鈎花鏤空針織背心250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 96、肩寬 35、衣長 54
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cimYL6671】實拍掛脖露肩假兩件針織上衣250904</t>
+  </si>
+  <si>
+    <t>F：胸圍 70、肩寬 35、袖長 60、衣長 54
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cim2688】實拍小眾復古設計款西裝外套250904</t>
+  </si>
+  <si>
+    <t>胸圍 96、肩寬 39、袖長 58、衣長 67
+胸圍 100、肩寬 41、袖長60、衣長68
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【cimYL916】實拍法式垂墜領顯瘦針織衫250904</t>
+  </si>
+  <si>
+    <t>胸圍 76、肩寬 34、袖長60、衣長49~53
 誤差 1–3 公分為正常，以實物為準。</t>
   </si>
 </sst>
@@ -196,7 +228,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -249,18 +281,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="PingFang SC"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,6 +292,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEFF2F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -286,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -315,20 +349,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,8 +650,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="141.75">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:3" ht="78.75">
+      <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -634,7 +659,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="110.25">
+    <row r="3" spans="1:3" ht="78.75">
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
@@ -643,8 +668,8 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" ht="141.75">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:3" ht="78.75">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -652,8 +677,8 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" ht="141.75">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:3" ht="110.25">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -661,188 +686,220 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" ht="141.75">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:3" ht="110.25">
+      <c r="A6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" ht="110.25">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" ht="141.75">
-      <c r="A7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" ht="141.75">
       <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" ht="110.25">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" ht="141.75">
-      <c r="A9" s="8" t="s">
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" ht="110.25">
+      <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" ht="141.75">
-      <c r="A10" s="7" t="s">
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" ht="120.75">
+      <c r="A11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" ht="141.75">
-      <c r="A11" s="8" t="s">
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" ht="78.75">
+      <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" ht="141.75">
-      <c r="A12" s="7" t="s">
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" ht="78.75">
+      <c r="A13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" ht="267.75">
-      <c r="A13" s="9" t="s">
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" ht="78.75">
+      <c r="A14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3" ht="141.75">
-      <c r="A14" s="9" t="s">
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" ht="105.75">
+      <c r="A15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3" ht="173.25">
-      <c r="A15" s="8" t="s">
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" ht="120.75">
+      <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3" ht="236.25">
-      <c r="A16" s="7" t="s">
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" ht="78.75">
+      <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" ht="141.75">
-      <c r="A17" s="7" t="s">
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" ht="78.75">
+      <c r="A18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" ht="94.5">
-      <c r="A18" s="8" t="s">
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" ht="78.75">
+      <c r="A19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" ht="94.5">
-      <c r="A19" s="7" t="s">
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" ht="78.75">
+      <c r="A20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" ht="94.5">
-      <c r="A20" s="8" t="s">
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" ht="78.75">
+      <c r="A21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" ht="78.75">
+      <c r="A22" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" ht="94.5">
-      <c r="A21" s="8" t="s">
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" ht="78.75">
+      <c r="A23" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
+    <row r="24" spans="1:3" ht="78.75">
+      <c r="A24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
+    <row r="25" spans="1:3" ht="78.75">
+      <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
+    <row r="26" spans="1:3" ht="78.75">
+      <c r="A26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
+    <row r="27" spans="1:3" ht="78.75">
+      <c r="A27" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+    <row r="28" spans="1:3" ht="105.75">
+      <c r="A28" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="8"/>
+    <row r="29" spans="1:3" ht="90">
+      <c r="A29" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3">

--- a/src/electron/crawler/config/小米粒夏日.xlsx
+++ b/src/electron/crawler/config/小米粒夏日.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\outsider\github\GF_playwright\src\electron\crawler\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1A1888-CE9A-427A-8D1A-388265E39782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF004B69-A1BA-480B-8F01-E8F6373ECB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>流水號</t>
   </si>
@@ -33,194 +33,201 @@
     <t>content</t>
   </si>
   <si>
-    <t>【cim038】實拍韓國QQ羊毛針織長背心（含羊毛13%）250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 94、肩寬 35、衣長 75
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim1258】實拍高級感簡約復古軟皮大容量單肩包250904</t>
-  </si>
-  <si>
-    <t>F：寬 46、高 24、底部 11
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim258】實拍韓國初秋小荷葉親膚天絲針織衫250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 94、肩寬 37、袖長 59、衣長 56
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2795】實拍設計款收腰繫帶長袖襯衫（純棉）250904</t>
-  </si>
-  <si>
-    <t>M：胸圍 106、肩寬 44、袖長 57、衣長 56
-L：胸圍 110、肩寬 46、袖長 59、衣長 58
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2796】實拍立領工裝抽繩寬鬆短風衣外套250904</t>
-  </si>
-  <si>
-    <t>M：胸圍 140、肩寬 59、袖長 52、衣長 54
-L：胸圍 144、肩寬 60、袖長 53、衣長 56
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2797】實拍舒適慵懶天絲混棉闊腿鬆緊刀褲250904</t>
-  </si>
-  <si>
-    <t>M：腰圍 66–82、臀圍 126、大腿圍 80、褲長 97
-L：腰圍 70–86、臀圍 130、大腿圍 84、褲長 99
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2798】實拍重工韓國設計款斜紋棉工裝褲250904</t>
-  </si>
-  <si>
-    <t>M：腰圍 66-78、臀圍 98、褲長 84
-L：腰圍 68-80、臀圍 102、褲長 86
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2799】實拍鬆緊腰下襬荷葉PU皮長褲250904</t>
-  </si>
-  <si>
-    <t>M：腰圍 64–82、臀圍 102、褲長 82
-L：腰圍 68–86、臀圍 106、褲長 84
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim519】實拍復古Polo領短袖針織衫+百褶短裙 套裝（羊毛6%）</t>
-  </si>
-  <si>
-    <t>上衣F：胸圍 86、肩寬 35、袖長 18、衣長 54
-半身裙：腰圍 62-76、臀圍 86、裙長 41
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim527】實拍初秋復古條紋POLO針織衫250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 90、肩寬 37、袖長 20、衣長 51
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim61601】實拍韓國極簡柔軟皮質單肩水桶包</t>
-  </si>
-  <si>
-    <t>F：寬 22、高 23、底部 17
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim6607】實拍韓國親膚棉羊6%針織背心250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 94、肩寬 36、衣長 57
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim677】實拍掛脖背心+圓領針織衫（含羊毛6%）250904</t>
-  </si>
-  <si>
-    <t>針織長袖F：胸圍 78、肩寬 35、袖長 55、衣長 54
-背心F：衣長 48
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim687】實拍慵懶深V鏤空針織罩衫+吊帶背心250904</t>
-  </si>
-  <si>
-    <t>針織罩衫F：胸圍 118、肩寬 63、袖長 49、衣長 48
-吊帶F：胸圍 70、衣長 47
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim695】實拍低調高級感的羊毛針織衫（含羊毛6%）250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 90、肩寬 38、袖長 54、衣長 51
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim698】實拍斜肩設計款顯瘦針織衫250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 72、肩寬 35、袖長 64、衣長 54
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim801】實拍高級感貝殼扣亨利款針織衫250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 72、肩寬 33、袖長 59、衣長 55
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim818】實拍韓系簡約鬆弛感披肩針織外套（含羊毛6%）250904</t>
-  </si>
-  <si>
-    <t>F：肩寬 36、袖長 60、衣長 54
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim8911】實拍絕美小眾復古軟皮大容量腋下托特包LD8911</t>
-  </si>
-  <si>
-    <t>F：寬 53、高 21、底部 39*14
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim907】實拍設計感一字肩顯瘦針織衫250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 70、袖長 59、衣長 54
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cimMB766】實拍慵懶復古中性寬鬆條紋POLO針織衫250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 108、肩寬 55、袖長 43、衣長 61
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cimMB775】實拍簡約中性條紋針織背心250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 90、肩寬 36、衣長 47
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cimOUT935】實拍高級感鈎花鏤空針織背心250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 96、肩寬 35、衣長 54
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cimYL6671】實拍掛脖露肩假兩件針織上衣250904</t>
-  </si>
-  <si>
-    <t>F：胸圍 70、肩寬 35、袖長 60、衣長 54
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cim2688】實拍小眾復古設計款西裝外套250904</t>
-  </si>
-  <si>
-    <t>胸圍 96、肩寬 39、袖長 58、衣長 67
-胸圍 100、肩寬 41、袖長60、衣長68
-誤差 1–3 公分為正常，以實物為準。</t>
-  </si>
-  <si>
-    <t>【cimYL916】實拍法式垂墜領顯瘦針織衫250904</t>
-  </si>
-  <si>
-    <t>胸圍 76、肩寬 34、袖長60、衣長49~53
+    <t>【YP119】實拍復古質感肌理針織背心250918</t>
+  </si>
+  <si>
+    <t>F：肩寬 33、袖長 /、胸圍 92、下擺圍 90、衣長 57
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82622】實拍設計款絨感立領收腰繫帶襯衫250918</t>
+  </si>
+  <si>
+    <t>M：肩寬 50、袖長 57、胸圍 112、下擺圍 112、衣長 60
+L：肩寬 51、袖長 58、胸圍 116、下擺圍 116、衣長 61
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y9823】實拍韓系簡約高腰闊腿八分褲+腰帶250918</t>
+  </si>
+  <si>
+    <t>M：腰圍 66、臀圍 100、大腿圍 70、褲腳圍 72、褲長 85
+L：腰圍 70、臀圍 104、大腿圍 72、褲腳圍 74、褲長 86
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP629】實拍韓系百褶高腰針織裙250918</t>
+  </si>
+  <si>
+    <t>F：腰圍 66、臀圍 /、下擺圍 /、裙長 88
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP205】實拍韓系針織開衫+吊帶背心P205250918</t>
+  </si>
+  <si>
+    <t>F (開衫)：肩寬 49、袖長 51、胸圍 112、下擺圍 106、衣長 62
+F (背心)：肩寬 24、袖長 /、胸圍 62、下擺圍 70、衣長 52
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82626】實拍天絲亞麻繫帶收腰襯衫250918</t>
+  </si>
+  <si>
+    <t>M：肩寬 53、袖長 55、胸圍 122、下擺圍 132、衣長 71
+L：肩寬 54、袖長 56、胸圍 126、下擺圍 136、衣長 72
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP222】實拍高級慵懶舒適拉鍊針織外套250918</t>
+  </si>
+  <si>
+    <t>F：肩寬 55、袖長 44、胸圍 126、下擺圍 122、衣長 62
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP225】實拍慵懶加厚針織毛衣外套250918</t>
+  </si>
+  <si>
+    <t>F：肩寬 63、袖長 43、胸圍 132、下擺圍 126、衣長 66
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82625】實拍韓國高質感立領長版風衣外套250918</t>
+  </si>
+  <si>
+    <t>M：肩寬 /、袖長 69、胸圍 128、腰圍 130、衣長 117
+L：肩寬 /、袖長 70、胸圍 132、腰圍 134、衣長 118
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82627】實拍復古圓領繫帶休閒襯衫(羊毛4%)250918</t>
+  </si>
+  <si>
+    <t>M：肩寬 39、袖長 58、胸圍 102、下擺圍 106、衣長 63
+L：肩寬 40、袖長 59、胸圍 106、下擺圍 110、衣長 64
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82612】實拍法式天絲長袖襯衫250918</t>
+  </si>
+  <si>
+    <t>M：肩寬 53、袖長 53、胸圍 118、下擺圍 118、衣長 65/69
+L：肩寬 54、袖長 54、胸圍 122、下擺圍 122、衣長 66/70
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y9822】實拍韓國天絲棉繫帶純色闊腿褲250918</t>
+  </si>
+  <si>
+    <t>M：腰圍 62、臀圍 116、大腿圍 74、褲腳圍 60、褲長 97
+L：腰圍 66、臀圍 120、大腿圍 76、褲腳圍 62、褲長 98
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82623】實拍簡約挺版顯瘦氣球直筒褲+腰帶250918</t>
+  </si>
+  <si>
+    <t>M：腰圍 62、臀圍 110、大腿圍 68、褲腳圍 60、褲長 96
+L：腰圍 66、臀圍 114、大腿圍 70、褲腳圍 62、褲長 97
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82608】實拍法式高級設計款斜門襟長袖襯衫250918</t>
+  </si>
+  <si>
+    <t>M：肩寬 48、袖長 54.5、胸圍 112、下擺圍 116、衣長 65/71
+L：肩寬 49、袖長 55.5、胸圍 116、下擺圍 120、衣長 66/72
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YG8109】實拍復古燈芯絨高腰A字七分闊腿褲+腰帶250918</t>
+  </si>
+  <si>
+    <t>後鬆緊腰圍
+M：腰圍 62、臀圍 100、大腿圍 72、褲腳圍 73、褲長 73
+L：腰圍 66、臀圍 104、大腿圍 74、褲腳圍 75、褲長 74
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YH2873】實拍復古牛仔長袖襯衫+背心套裝250918</t>
+  </si>
+  <si>
+    <t>F (襯衫)：肩寬 44、袖長 61、胸圍 104、下擺圍 109、衣長 72/76.5
+F (背心)：肩寬 30、袖長 /、胸圍 72、下擺圍 72、衣長 52
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YH3509】實拍韓版寬鬆顯瘦背心+豹紋方巾250918</t>
+  </si>
+  <si>
+    <t>F：肩寬 40、袖長 /、胸圍 110、下擺圍 106、衣長 59
+豹紋方巾“60*60
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82630】實拍高腰綁帶不規則時髦西裝褲250918</t>
+  </si>
+  <si>
+    <t>S：腰圍 60、臀圍 86、大腿圍 60、褲腳圍 58、褲長 100
+M：腰圍 64、臀圍 90、大腿圍 62、褲腳圍 60、褲長 101
+L：腰圍 68、臀圍 94、大腿圍 64、褲腳圍 62、褲長 102
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y716】實拍韓系黑白條紋純棉長袖T恤250918</t>
+  </si>
+  <si>
+    <t>F：肩寬 50、袖長 55、胸圍 106、下擺圍 110、衣長 64
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YP220】實拍簡約針織毛衣+直筒針織裙250918</t>
+  </si>
+  <si>
+    <t>F (上衣)：肩寬 48、袖長 48、胸圍 110、下擺圍 114、衣長 67
+F (半身裙)：腰圍 64、臀圍 88、下擺圍 110、裙長 80
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82563】實拍秋季長袖打底衫+針織背心+腰帶250918</t>
+  </si>
+  <si>
+    <t>M (T恤)：肩寬 35、袖長 60、胸圍 78、腰圍 70、衣長 52
+L (T恤)：肩寬 36、袖長 61、胸圍 82、腰圍 74、衣長 53
+M (馬甲)：肩寬 39、袖長 /、胸圍 94、下擺圍 104、衣長 63/70
+L (馬甲)：肩寬 40、袖長 /、胸圍 98、下擺圍 108、衣長 64/71
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y78251】實拍初秋棉質高腰A字微氣球裙+腰帶小白250918</t>
+  </si>
+  <si>
+    <t>M：腰圍 62、臀圍 102、下擺圍 154、裙長 83
+L：腰圍 66、臀圍 106、下擺圍 158、裙長 84
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【YW2502】實拍秋季質感豹紋時髦絲巾250918</t>
+  </si>
+  <si>
+    <t>尺寸：66*66 cm
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82628】實拍綁帶收腰高級感天絲襯衫250918</t>
+  </si>
+  <si>
+    <t>M：肩寬 48、袖長 56、胸圍 102、下擺圍 118、衣長 63
+L：肩寬 49、袖長 57、胸圍 106、下擺圍 122、衣長 64
+誤差 1–3 公分為正常，以實物為準。</t>
+  </si>
+  <si>
+    <t>【Y82629】實拍韓國設計款立領純棉襯衫250918</t>
+  </si>
+  <si>
+    <t>M：肩寬 50、袖長 54、胸圍 112、下擺圍 112、衣長 65/70
+L：肩寬 51、袖長 55、胸圍 116、下擺圍 116、衣長 66/71
 誤差 1–3 公分為正常，以實物為準。</t>
   </si>
 </sst>
@@ -650,256 +657,244 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="78.75">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:3" ht="64.900000000000006">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="78.75">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:3" ht="115.9">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" ht="78.75">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:3" ht="115.9">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" ht="110.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:3" ht="64.900000000000006">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" ht="110.25">
-      <c r="A6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>9</v>
+    <row r="6" spans="1:3" ht="115.9">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" ht="110.25">
-      <c r="A7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>11</v>
+    <row r="7" spans="1:3" ht="115.9">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" ht="141.75">
-      <c r="A8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>13</v>
+    <row r="8" spans="1:3" ht="77.650000000000006">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" ht="110.25">
-      <c r="A9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>15</v>
+    <row r="9" spans="1:3" ht="77.650000000000006">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="110.25">
-      <c r="A10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>17</v>
+    <row r="10" spans="1:3" ht="90.4">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" ht="120.75">
-      <c r="A11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>19</v>
+    <row r="11" spans="1:3" ht="115.9">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" ht="78.75">
-      <c r="A12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>21</v>
+    <row r="12" spans="1:3" ht="115.9">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" ht="78.75">
-      <c r="A13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>23</v>
+    <row r="13" spans="1:3" ht="115.9">
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" ht="78.75">
-      <c r="A14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>25</v>
+    <row r="14" spans="1:3" ht="115.9">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" ht="105.75">
-      <c r="A15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>27</v>
+    <row r="15" spans="1:3" ht="115.9">
+      <c r="A15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" ht="120.75">
-      <c r="A16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>29</v>
+    <row r="16" spans="1:3" ht="128.65">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" ht="78.75">
-      <c r="A17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>31</v>
+    <row r="17" spans="1:3" ht="115.9">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" ht="78.75">
-      <c r="A18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>33</v>
+    <row r="18" spans="1:3" ht="90.4">
+      <c r="A18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" ht="78.75">
-      <c r="A19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>35</v>
+    <row r="19" spans="1:3" ht="154.15">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" ht="78.75">
-      <c r="A20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>37</v>
+    <row r="20" spans="1:3" ht="77.650000000000006">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" ht="78.75">
-      <c r="A21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>37</v>
+    <row r="21" spans="1:3" ht="115.9">
+      <c r="A21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" ht="78.75">
-      <c r="A22" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>39</v>
+    <row r="22" spans="1:3" ht="192.4">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" ht="78.75">
-      <c r="A23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>41</v>
+    <row r="23" spans="1:3" ht="115.9">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" ht="78.75">
-      <c r="A24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>43</v>
+    <row r="24" spans="1:3" ht="52.15">
+      <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="78.75">
-      <c r="A25" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>45</v>
+    <row r="25" spans="1:3" ht="115.9">
+      <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="78.75">
-      <c r="A26" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>47</v>
+    <row r="26" spans="1:3" ht="115.9">
+      <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" ht="78.75">
-      <c r="A27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>49</v>
-      </c>
+    <row r="27" spans="1:3">
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" ht="105.75">
-      <c r="A28" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>51</v>
-      </c>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" ht="90">
-      <c r="A29" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>53</v>
-      </c>
+    <row r="29" spans="1:3">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3">
